--- a/Web/TestCasesWeb/FicherosSeguimiento.xlsx
+++ b/Web/TestCasesWeb/FicherosSeguimiento.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2839DA7-69DA-4A69-AADF-EBC6E7790E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA646AE-D57B-41CD-85C1-0766DCD1DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="780" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>Num</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>pte</t>
-  </si>
-  <si>
     <t>LOG001</t>
   </si>
   <si>
@@ -76,36 +73,6 @@
     <t>La opción se tiene q llamar "Ficheros de seguimiento" en castellano, no logs</t>
   </si>
   <si>
-    <t>Create log</t>
-  </si>
-  <si>
-    <t>Modify log</t>
-  </si>
-  <si>
-    <t>Delete log</t>
-  </si>
-  <si>
-    <t>1. The log is created.</t>
-  </si>
-  <si>
-    <t>1. The log is modified.</t>
-  </si>
-  <si>
-    <t>1. The log is deleted.</t>
-  </si>
-  <si>
-    <t>Create log: cancel operation</t>
-  </si>
-  <si>
-    <t>Modify log: cancel operation</t>
-  </si>
-  <si>
-    <t>Delete log: cancel operation</t>
-  </si>
-  <si>
-    <t>1. The operation is cancelled.</t>
-  </si>
-  <si>
     <t>LOG005</t>
   </si>
   <si>
@@ -113,6 +80,45 @@
   </si>
   <si>
     <t>LOG007</t>
+  </si>
+  <si>
+    <t>Log by restaurant</t>
+  </si>
+  <si>
+    <t>Filter: show</t>
+  </si>
+  <si>
+    <t>Filter: hide</t>
+  </si>
+  <si>
+    <t>Filter: update</t>
+  </si>
+  <si>
+    <t>Filter: select action</t>
+  </si>
+  <si>
+    <t>Filter: Select entity</t>
+  </si>
+  <si>
+    <t>Filter: select origin</t>
+  </si>
+  <si>
+    <t>Filter: Select from</t>
+  </si>
+  <si>
+    <t>Filter: Select to</t>
+  </si>
+  <si>
+    <t>Filter: Clear</t>
+  </si>
+  <si>
+    <t>Filter: See</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>No se controla que la fecha "Hasta" sea superior a la fecha "Desde": Logs001.jpg</t>
   </si>
 </sst>
 </file>
@@ -553,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -594,23 +600,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -618,18 +624,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H3" s="6"/>
     </row>
@@ -638,18 +642,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -658,18 +660,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -678,18 +678,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H6" s="6"/>
     </row>
@@ -698,18 +696,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -718,24 +714,114 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/Web/TestCasesWeb/FicherosSeguimiento.xlsx
+++ b/Web/TestCasesWeb/FicherosSeguimiento.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA646AE-D57B-41CD-85C1-0766DCD1DC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="780" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
